--- a/artfynd/A 17456-2026 artfynd.xlsx
+++ b/artfynd/A 17456-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134667257</v>
+        <v>135259564</v>
       </c>
       <c r="B2" t="n">
-        <v>107943</v>
+        <v>96410</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219933</v>
+        <v>2812</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfot</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antennaria dioica</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Gaertn.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490011</v>
+        <v>490155</v>
       </c>
       <c r="R2" t="n">
-        <v>6996049</v>
+        <v>6995762</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -740,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134667264</v>
+        <v>135259731</v>
       </c>
       <c r="B3" t="n">
-        <v>108205</v>
+        <v>96410</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220083</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490172</v>
+        <v>490021</v>
       </c>
       <c r="R3" t="n">
-        <v>6995778</v>
+        <v>6995979</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -842,17 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,48 +869,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134667203</v>
+        <v>135260408</v>
       </c>
       <c r="B4" t="n">
-        <v>99099</v>
+        <v>43314</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220093</v>
+        <v>201146</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Schneider, 1792)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490158</v>
+        <v>489967</v>
       </c>
       <c r="R4" t="n">
-        <v>6995775</v>
+        <v>6996029</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -944,17 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>3 ex</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134667289</v>
+        <v>135251761</v>
       </c>
       <c r="B5" t="n">
-        <v>110150</v>
+        <v>99197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,34 +977,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220294</v>
+        <v>219811</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällskära</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saussurea alpina</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) DC.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490122</v>
+        <v>490003</v>
       </c>
       <c r="R5" t="n">
-        <v>6995824</v>
+        <v>6995966</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1046,17 +1035,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134667293</v>
+        <v>135251864</v>
       </c>
       <c r="B6" t="n">
-        <v>110150</v>
+        <v>99197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,34 +1078,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220294</v>
+        <v>219811</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällskära</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saussurea alpina</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) DC.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490042</v>
+        <v>490193</v>
       </c>
       <c r="R6" t="n">
-        <v>6995958</v>
+        <v>6995759</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1148,17 +1136,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1168,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134667359</v>
+        <v>135251865</v>
       </c>
       <c r="B7" t="n">
-        <v>110150</v>
+        <v>99197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,34 +1179,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220294</v>
+        <v>219811</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällskära</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saussurea alpina</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) DC.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490132</v>
+        <v>490185</v>
       </c>
       <c r="R7" t="n">
-        <v>6995842</v>
+        <v>6995767</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1250,17 +1237,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,10 +1269,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134667263</v>
+        <v>135251867</v>
       </c>
       <c r="B8" t="n">
-        <v>100806</v>
+        <v>99197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,34 +1280,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222584</v>
+        <v>219811</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bergsslok</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Melica nutans</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490137</v>
+        <v>490175</v>
       </c>
       <c r="R8" t="n">
-        <v>6995833</v>
+        <v>6995781</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1352,17 +1338,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134667291</v>
+        <v>135251868</v>
       </c>
       <c r="B9" t="n">
-        <v>100806</v>
+        <v>99197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,34 +1381,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222584</v>
+        <v>219811</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bergsslok</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Melica nutans</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490082</v>
+        <v>490171</v>
       </c>
       <c r="R9" t="n">
-        <v>6995886</v>
+        <v>6995790</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1454,17 +1439,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134667258</v>
+        <v>135251869</v>
       </c>
       <c r="B10" t="n">
-        <v>99472</v>
+        <v>99197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,34 +1482,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222812</v>
+        <v>219811</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490025</v>
+        <v>490109</v>
       </c>
       <c r="R10" t="n">
-        <v>6996032</v>
+        <v>6995869</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1556,17 +1540,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,10 +1572,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134667286</v>
+        <v>135251871</v>
       </c>
       <c r="B11" t="n">
-        <v>99472</v>
+        <v>99197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,34 +1583,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222812</v>
+        <v>219811</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490160</v>
+        <v>490100</v>
       </c>
       <c r="R11" t="n">
-        <v>6995755</v>
+        <v>6995889</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1658,17 +1641,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,10 +1673,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134667288</v>
+        <v>135251873</v>
       </c>
       <c r="B12" t="n">
-        <v>102871</v>
+        <v>99197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1706,34 +1684,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223037</v>
+        <v>219811</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Humleblomster</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Geum rivale</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490122</v>
+        <v>490070</v>
       </c>
       <c r="R12" t="n">
-        <v>6995824</v>
+        <v>6995932</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1760,17 +1742,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1794,6 +1771,8306 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135251876</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>490049</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6995960</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135251878</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>490030</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6996016</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135251879</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>490020</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6996030</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135251880</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>490019</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6996035</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135251881</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>490014</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6996047</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135251882</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>490011</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6996051</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135251884</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>490003</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6996072</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135251885</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>490009</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6996061</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135251886</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>489996</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6996048</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135251888</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>490010</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6996013</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135251889</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>490016</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6996007</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135251891</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>490024</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6995989</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135251892</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>490034</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6995967</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135251893</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>490074</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6995898</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135251894</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>490081</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6995890</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135251895</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>490083</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6995883</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135251896</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>490088</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6995880</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135251897</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>490090</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6995873</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135251899</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>490102</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6995859</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135251901</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>490105</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6995849</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135251902</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>490111</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6995844</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135251904</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>490111</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6995837</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135251905</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>490117</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6995827</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135251906</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>490124</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6995819</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135251907</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>490125</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6995817</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135251909</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>490131</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6995807</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135251910</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>490134</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6995801</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135251911</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>490140</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6995797</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135251912</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>490140</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6995790</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135251913</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>490146</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6995783</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135251914</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>490154</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6995774</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135251915</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>490159</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6995770</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135251916</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>490163</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6995766</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135251917</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>490173</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6995759</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135251918</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99197</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>490176</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6995750</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135251730</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>490137</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6995784</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135251732</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>490137</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6995777</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Noterad</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135251734</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>490143</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6995765</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135251736</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>490148</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6995762</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135251866</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>490173</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6995778</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135251874</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>490050</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6995959</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135251898</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>490090</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6995871</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135251900</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>490105</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6995849</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135251903</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>490111</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6995840</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135251908</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99219</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>490129</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6995810</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>134667257</v>
+      </c>
+      <c r="B58" t="n">
+        <v>107943</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>219933</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Kattfot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Antennaria dioica</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>490011</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6996049</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>134667264</v>
+      </c>
+      <c r="B59" t="n">
+        <v>108205</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>490172</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6995778</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135259562</v>
+      </c>
+      <c r="B60" t="n">
+        <v>108205</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>490137</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6995770</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135259708</v>
+      </c>
+      <c r="B61" t="n">
+        <v>108205</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>489986</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6996067</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135259727</v>
+      </c>
+      <c r="B62" t="n">
+        <v>108205</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>490028</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6995963</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135259737</v>
+      </c>
+      <c r="B63" t="n">
+        <v>108205</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>489990</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6996028</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>134667203</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99099</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>490158</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6995775</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>3 ex</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135251727</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99099</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>490159</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6995759</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135259548</v>
+      </c>
+      <c r="B66" t="n">
+        <v>108274</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220102</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Kärrfibbla</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Crepis paludosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>490145</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6995771</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>134667289</v>
+      </c>
+      <c r="B67" t="n">
+        <v>110150</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220294</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Fjällskära</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Saussurea alpina</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) DC.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>490122</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6995824</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>134667293</v>
+      </c>
+      <c r="B68" t="n">
+        <v>110150</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220294</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Fjällskära</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Saussurea alpina</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) DC.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>490042</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6995958</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>134667359</v>
+      </c>
+      <c r="B69" t="n">
+        <v>110150</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220294</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Fjällskära</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Saussurea alpina</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) DC.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>490132</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6995842</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135259550</v>
+      </c>
+      <c r="B70" t="n">
+        <v>103762</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>490110</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6995828</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135259552</v>
+      </c>
+      <c r="B71" t="n">
+        <v>103762</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>490121</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6995803</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>135259553</v>
+      </c>
+      <c r="B72" t="n">
+        <v>104707</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>490135</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6995783</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135259728</v>
+      </c>
+      <c r="B73" t="n">
+        <v>104707</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>490023</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6995970</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135259549</v>
+      </c>
+      <c r="B74" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>490110</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6995828</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135259551</v>
+      </c>
+      <c r="B75" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>490118</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6995807</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135259566</v>
+      </c>
+      <c r="B76" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>490155</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6995762</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>135259724</v>
+      </c>
+      <c r="B77" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>490047</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6995923</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>135259726</v>
+      </c>
+      <c r="B78" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>490028</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6995963</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>135259730</v>
+      </c>
+      <c r="B79" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>490021</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6995979</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>134667263</v>
+      </c>
+      <c r="B80" t="n">
+        <v>100806</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>490137</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6995833</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>134667291</v>
+      </c>
+      <c r="B81" t="n">
+        <v>100806</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>490082</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6995886</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>135259556</v>
+      </c>
+      <c r="B82" t="n">
+        <v>100806</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>490135</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6995775</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>135259722</v>
+      </c>
+      <c r="B83" t="n">
+        <v>100806</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>490047</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6995923</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>135259729</v>
+      </c>
+      <c r="B84" t="n">
+        <v>101305</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>490021</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6995979</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>134667258</v>
+      </c>
+      <c r="B85" t="n">
+        <v>99472</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>490025</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6996032</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>134667286</v>
+      </c>
+      <c r="B86" t="n">
+        <v>99472</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>490160</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6995755</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>135259542</v>
+      </c>
+      <c r="B87" t="n">
+        <v>99472</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>490180</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6995779</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>135259560</v>
+      </c>
+      <c r="B88" t="n">
+        <v>99472</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>490137</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6995770</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>134667288</v>
+      </c>
+      <c r="B89" t="n">
+        <v>102871</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>223037</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Humleblomster</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Geum rivale</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>490122</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6995824</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>135259565</v>
+      </c>
+      <c r="B90" t="n">
+        <v>102871</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>223037</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Humleblomster</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Geum rivale</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>490141</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6995767</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>135259709</v>
+      </c>
+      <c r="B91" t="n">
+        <v>102871</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>223037</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Humleblomster</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Geum rivale</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>489988</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6996054</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>135259720</v>
+      </c>
+      <c r="B92" t="n">
+        <v>102871</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>223037</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Humleblomster</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Geum rivale</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>490075</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6995889</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>135259546</v>
+      </c>
+      <c r="B93" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>490150</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6995761</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>135251877</v>
+      </c>
+      <c r="B94" t="n">
+        <v>99105</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>223572</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Blodnycklar</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Dactylorhiza incarnata var. cruenta</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(O F.Müll.) Hyl.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>490029</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6996006</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>135259713</v>
+      </c>
+      <c r="B95" t="n">
+        <v>95840</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>1004672</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Källmossor</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Philonotis</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Brid.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>489985</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6996008</v>
+      </c>
+      <c r="S95" t="n">
+        <v>5</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17456-2026 artfynd.xlsx
+++ b/artfynd/A 17456-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY95"/>
+  <dimension ref="A1:AZ95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259564</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259731</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135260408</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251761</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251864</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1266,6 +1296,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251865</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1367,6 +1402,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251867</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,6 +1508,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251868</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1569,6 +1614,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251869</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1670,6 +1720,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251871</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1771,6 +1826,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251873</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1872,6 +1932,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251876</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1973,6 +2038,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251878</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2074,6 +2144,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251879</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2175,6 +2250,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251880</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2276,6 +2356,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251881</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2377,6 +2462,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251882</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2478,6 +2568,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251884</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2579,6 +2674,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251885</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2680,6 +2780,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251886</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2781,6 +2886,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251888</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2882,6 +2992,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251889</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2983,6 +3098,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251891</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3084,6 +3204,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251892</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3185,6 +3310,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251893</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3286,6 +3416,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251894</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3387,6 +3522,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251895</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3488,6 +3628,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251896</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3589,6 +3734,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251897</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3690,6 +3840,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251899</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3791,6 +3946,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251901</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3892,6 +4052,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251902</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3993,6 +4158,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251904</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4094,6 +4264,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251905</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4195,6 +4370,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251906</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4296,6 +4476,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251907</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4397,6 +4582,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251909</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4498,6 +4688,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251910</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4599,6 +4794,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251911</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4700,6 +4900,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251912</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4801,6 +5006,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251913</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4902,6 +5112,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251914</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5003,6 +5218,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251915</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5104,6 +5324,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251916</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5205,6 +5430,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251917</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5306,6 +5536,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251918</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5407,6 +5642,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251730</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5509,6 +5749,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251732</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5610,6 +5855,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251734</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5711,6 +5961,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251736</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5812,6 +6067,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251866</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5913,6 +6173,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251874</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6014,6 +6279,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251898</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6115,6 +6385,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251900</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6216,6 +6491,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251903</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6317,6 +6597,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251908</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6419,6 +6704,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134667257</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6521,6 +6811,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134667264</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6618,6 +6913,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259562</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6715,6 +7015,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259708</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6812,6 +7117,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259727</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6909,6 +7219,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259737</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7011,6 +7326,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134667203</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7112,6 +7432,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251727</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7209,6 +7534,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259548</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7311,6 +7641,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134667289</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7413,6 +7748,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134667293</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7515,6 +7855,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134667359</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7612,6 +7957,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259550</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7709,6 +8059,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259552</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7806,6 +8161,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259553</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7903,6 +8263,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259728</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8000,6 +8365,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259549</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8097,6 +8467,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259551</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8194,6 +8569,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259566</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8291,6 +8671,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259724</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8388,6 +8773,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259726</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8485,6 +8875,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259730</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8587,6 +8982,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134667263</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8689,6 +9089,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134667291</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8786,6 +9191,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259556</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8883,6 +9293,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259722</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8980,6 +9395,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259729</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9082,6 +9502,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134667258</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9184,6 +9609,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134667286</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9286,6 +9716,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259542</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9383,6 +9818,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259560</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9485,6 +9925,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134667288</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9582,6 +10027,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259565</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9679,6 +10129,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259709</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9776,6 +10231,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259720</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9873,6 +10333,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259546</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9974,6 +10439,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251877</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10071,8 +10541,109 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259713</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 17456-2026 artfynd.xlsx
+++ b/artfynd/A 17456-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135259564</v>
       </c>
       <c r="B2" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135259731</v>
       </c>
       <c r="B3" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135260408</v>
       </c>
       <c r="B4" t="n">
-        <v>43314</v>
+        <v>43319</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135251761</v>
       </c>
       <c r="B5" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>135251864</v>
       </c>
       <c r="B6" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>135251865</v>
       </c>
       <c r="B7" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>135251867</v>
       </c>
       <c r="B8" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>135251868</v>
       </c>
       <c r="B9" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>135251869</v>
       </c>
       <c r="B10" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>135251871</v>
       </c>
       <c r="B11" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>135251873</v>
       </c>
       <c r="B12" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>135251876</v>
       </c>
       <c r="B13" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>135251878</v>
       </c>
       <c r="B14" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>135251879</v>
       </c>
       <c r="B15" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>135251880</v>
       </c>
       <c r="B16" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>135251881</v>
       </c>
       <c r="B17" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>135251882</v>
       </c>
       <c r="B18" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>135251884</v>
       </c>
       <c r="B19" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>135251885</v>
       </c>
       <c r="B20" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>135251886</v>
       </c>
       <c r="B21" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>135251888</v>
       </c>
       <c r="B22" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>135251889</v>
       </c>
       <c r="B23" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>135251891</v>
       </c>
       <c r="B24" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>135251892</v>
       </c>
       <c r="B25" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>135251893</v>
       </c>
       <c r="B26" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>135251894</v>
       </c>
       <c r="B27" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>135251895</v>
       </c>
       <c r="B28" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>135251896</v>
       </c>
       <c r="B29" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>135251897</v>
       </c>
       <c r="B30" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>135251899</v>
       </c>
       <c r="B31" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>135251901</v>
       </c>
       <c r="B32" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>135251902</v>
       </c>
       <c r="B33" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>135251904</v>
       </c>
       <c r="B34" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>135251905</v>
       </c>
       <c r="B35" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>135251906</v>
       </c>
       <c r="B36" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>135251907</v>
       </c>
       <c r="B37" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>135251909</v>
       </c>
       <c r="B38" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>135251910</v>
       </c>
       <c r="B39" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>135251911</v>
       </c>
       <c r="B40" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>135251912</v>
       </c>
       <c r="B41" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>135251913</v>
       </c>
       <c r="B42" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>135251914</v>
       </c>
       <c r="B43" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>135251915</v>
       </c>
       <c r="B44" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>135251916</v>
       </c>
       <c r="B45" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         <v>135251917</v>
       </c>
       <c r="B46" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>135251918</v>
       </c>
       <c r="B47" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>135251730</v>
       </c>
       <c r="B48" t="n">
-        <v>99219</v>
+        <v>99266</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         <v>135251732</v>
       </c>
       <c r="B49" t="n">
-        <v>99219</v>
+        <v>99266</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>135251734</v>
       </c>
       <c r="B50" t="n">
-        <v>99219</v>
+        <v>99266</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>135251736</v>
       </c>
       <c r="B51" t="n">
-        <v>99219</v>
+        <v>99266</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>135251866</v>
       </c>
       <c r="B52" t="n">
-        <v>99219</v>
+        <v>99266</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6078,7 +6078,7 @@
         <v>135251874</v>
       </c>
       <c r="B53" t="n">
-        <v>99219</v>
+        <v>99266</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>135251898</v>
       </c>
       <c r="B54" t="n">
-        <v>99219</v>
+        <v>99266</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>135251900</v>
       </c>
       <c r="B55" t="n">
-        <v>99219</v>
+        <v>99266</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>135251903</v>
       </c>
       <c r="B56" t="n">
-        <v>99219</v>
+        <v>99266</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>135251908</v>
       </c>
       <c r="B57" t="n">
-        <v>99219</v>
+        <v>99266</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>135259562</v>
       </c>
       <c r="B60" t="n">
-        <v>108205</v>
+        <v>108260</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>135259708</v>
       </c>
       <c r="B61" t="n">
-        <v>108205</v>
+        <v>108260</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>135259727</v>
       </c>
       <c r="B62" t="n">
-        <v>108205</v>
+        <v>108260</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>135259737</v>
       </c>
       <c r="B63" t="n">
-        <v>108205</v>
+        <v>108260</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>135251727</v>
       </c>
       <c r="B65" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>135259548</v>
       </c>
       <c r="B66" t="n">
-        <v>108274</v>
+        <v>108330</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>135259550</v>
       </c>
       <c r="B70" t="n">
-        <v>103762</v>
+        <v>103813</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>135259552</v>
       </c>
       <c r="B71" t="n">
-        <v>103762</v>
+        <v>103813</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         <v>135259553</v>
       </c>
       <c r="B72" t="n">
-        <v>104707</v>
+        <v>104761</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         <v>135259728</v>
       </c>
       <c r="B73" t="n">
-        <v>104707</v>
+        <v>104761</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>135259549</v>
       </c>
       <c r="B74" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>135259551</v>
       </c>
       <c r="B75" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>135259566</v>
       </c>
       <c r="B76" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>135259724</v>
       </c>
       <c r="B77" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>135259726</v>
       </c>
       <c r="B78" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>135259730</v>
       </c>
       <c r="B79" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>135259556</v>
       </c>
       <c r="B82" t="n">
-        <v>100806</v>
+        <v>100854</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>135259722</v>
       </c>
       <c r="B83" t="n">
-        <v>100806</v>
+        <v>100854</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>135259729</v>
       </c>
       <c r="B84" t="n">
-        <v>101305</v>
+        <v>101353</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         <v>135259542</v>
       </c>
       <c r="B87" t="n">
-        <v>99472</v>
+        <v>99519</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>135259560</v>
       </c>
       <c r="B88" t="n">
-        <v>99472</v>
+        <v>99519</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>135259565</v>
       </c>
       <c r="B90" t="n">
-        <v>102871</v>
+        <v>102922</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
         <v>135259709</v>
       </c>
       <c r="B91" t="n">
-        <v>102871</v>
+        <v>102922</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>135259720</v>
       </c>
       <c r="B92" t="n">
-        <v>102871</v>
+        <v>102922</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>135259546</v>
       </c>
       <c r="B93" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>135251877</v>
       </c>
       <c r="B94" t="n">
-        <v>99105</v>
+        <v>99152</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>135259713</v>
       </c>
       <c r="B95" t="n">
-        <v>95840</v>
+        <v>95884</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 17456-2026 artfynd.xlsx
+++ b/artfynd/A 17456-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135259564</v>
       </c>
       <c r="B2" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135259731</v>
       </c>
       <c r="B3" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135251761</v>
       </c>
       <c r="B5" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>135251864</v>
       </c>
       <c r="B6" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>135251865</v>
       </c>
       <c r="B7" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>135251867</v>
       </c>
       <c r="B8" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>135251868</v>
       </c>
       <c r="B9" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>135251869</v>
       </c>
       <c r="B10" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>135251871</v>
       </c>
       <c r="B11" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>135251873</v>
       </c>
       <c r="B12" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>135251876</v>
       </c>
       <c r="B13" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>135251878</v>
       </c>
       <c r="B14" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>135251879</v>
       </c>
       <c r="B15" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>135251880</v>
       </c>
       <c r="B16" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>135251881</v>
       </c>
       <c r="B17" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>135251882</v>
       </c>
       <c r="B18" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>135251884</v>
       </c>
       <c r="B19" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>135251885</v>
       </c>
       <c r="B20" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>135251886</v>
       </c>
       <c r="B21" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>135251888</v>
       </c>
       <c r="B22" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>135251889</v>
       </c>
       <c r="B23" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>135251891</v>
       </c>
       <c r="B24" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>135251892</v>
       </c>
       <c r="B25" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>135251893</v>
       </c>
       <c r="B26" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>135251894</v>
       </c>
       <c r="B27" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>135251895</v>
       </c>
       <c r="B28" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>135251896</v>
       </c>
       <c r="B29" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>135251897</v>
       </c>
       <c r="B30" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>135251899</v>
       </c>
       <c r="B31" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>135251901</v>
       </c>
       <c r="B32" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>135251902</v>
       </c>
       <c r="B33" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>135251904</v>
       </c>
       <c r="B34" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>135251905</v>
       </c>
       <c r="B35" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>135251906</v>
       </c>
       <c r="B36" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>135251907</v>
       </c>
       <c r="B37" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>135251909</v>
       </c>
       <c r="B38" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>135251910</v>
       </c>
       <c r="B39" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>135251911</v>
       </c>
       <c r="B40" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>135251912</v>
       </c>
       <c r="B41" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>135251913</v>
       </c>
       <c r="B42" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>135251914</v>
       </c>
       <c r="B43" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>135251915</v>
       </c>
       <c r="B44" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>135251916</v>
       </c>
       <c r="B45" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         <v>135251917</v>
       </c>
       <c r="B46" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>135251918</v>
       </c>
       <c r="B47" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>135251730</v>
       </c>
       <c r="B48" t="n">
-        <v>99266</v>
+        <v>99293</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         <v>135251732</v>
       </c>
       <c r="B49" t="n">
-        <v>99266</v>
+        <v>99293</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>135251734</v>
       </c>
       <c r="B50" t="n">
-        <v>99266</v>
+        <v>99293</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>135251736</v>
       </c>
       <c r="B51" t="n">
-        <v>99266</v>
+        <v>99293</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>135251866</v>
       </c>
       <c r="B52" t="n">
-        <v>99266</v>
+        <v>99293</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6078,7 +6078,7 @@
         <v>135251874</v>
       </c>
       <c r="B53" t="n">
-        <v>99266</v>
+        <v>99293</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>135251898</v>
       </c>
       <c r="B54" t="n">
-        <v>99266</v>
+        <v>99293</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>135251900</v>
       </c>
       <c r="B55" t="n">
-        <v>99266</v>
+        <v>99293</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>135251903</v>
       </c>
       <c r="B56" t="n">
-        <v>99266</v>
+        <v>99293</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>135251908</v>
       </c>
       <c r="B57" t="n">
-        <v>99266</v>
+        <v>99293</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>135259562</v>
       </c>
       <c r="B60" t="n">
-        <v>108260</v>
+        <v>108287</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>135259708</v>
       </c>
       <c r="B61" t="n">
-        <v>108260</v>
+        <v>108287</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>135259727</v>
       </c>
       <c r="B62" t="n">
-        <v>108260</v>
+        <v>108287</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>135259737</v>
       </c>
       <c r="B63" t="n">
-        <v>108260</v>
+        <v>108287</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>135251727</v>
       </c>
       <c r="B65" t="n">
-        <v>99146</v>
+        <v>99173</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>135259548</v>
       </c>
       <c r="B66" t="n">
-        <v>108330</v>
+        <v>108357</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>135259550</v>
       </c>
       <c r="B70" t="n">
-        <v>103813</v>
+        <v>103840</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>135259552</v>
       </c>
       <c r="B71" t="n">
-        <v>103813</v>
+        <v>103840</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         <v>135259553</v>
       </c>
       <c r="B72" t="n">
-        <v>104761</v>
+        <v>104788</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         <v>135259728</v>
       </c>
       <c r="B73" t="n">
-        <v>104761</v>
+        <v>104788</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>135259549</v>
       </c>
       <c r="B74" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>135259551</v>
       </c>
       <c r="B75" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>135259566</v>
       </c>
       <c r="B76" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>135259724</v>
       </c>
       <c r="B77" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>135259726</v>
       </c>
       <c r="B78" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>135259730</v>
       </c>
       <c r="B79" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>135259556</v>
       </c>
       <c r="B82" t="n">
-        <v>100854</v>
+        <v>100881</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>135259722</v>
       </c>
       <c r="B83" t="n">
-        <v>100854</v>
+        <v>100881</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>135259729</v>
       </c>
       <c r="B84" t="n">
-        <v>101353</v>
+        <v>101380</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         <v>135259542</v>
       </c>
       <c r="B87" t="n">
-        <v>99519</v>
+        <v>99546</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>135259560</v>
       </c>
       <c r="B88" t="n">
-        <v>99519</v>
+        <v>99546</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>135259565</v>
       </c>
       <c r="B90" t="n">
-        <v>102922</v>
+        <v>102949</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
         <v>135259709</v>
       </c>
       <c r="B91" t="n">
-        <v>102922</v>
+        <v>102949</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>135259720</v>
       </c>
       <c r="B92" t="n">
-        <v>102922</v>
+        <v>102949</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>135259546</v>
       </c>
       <c r="B93" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>135251877</v>
       </c>
       <c r="B94" t="n">
-        <v>99152</v>
+        <v>99179</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>135259713</v>
       </c>
       <c r="B95" t="n">
-        <v>95884</v>
+        <v>95911</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 17456-2026 artfynd.xlsx
+++ b/artfynd/A 17456-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134667257</v>
+        <v>135259564</v>
       </c>
       <c r="B2" t="n">
-        <v>107943</v>
+        <v>96486</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219933</v>
+        <v>2812</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfot</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antennaria dioica</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Gaertn.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490011</v>
+        <v>490155</v>
       </c>
       <c r="R2" t="n">
-        <v>6996049</v>
+        <v>6995762</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,17 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,16 +776,16 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134667257</t>
+          <t>https://artportalen.se/Sighting/135259564</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134667264</v>
+        <v>135259731</v>
       </c>
       <c r="B3" t="n">
-        <v>108205</v>
+        <v>96486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220083</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490172</v>
+        <v>490021</v>
       </c>
       <c r="R3" t="n">
-        <v>6995778</v>
+        <v>6995979</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,17 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,54 +878,54 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134667264</t>
+          <t>https://artportalen.se/Sighting/135259731</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134667203</v>
+        <v>135260408</v>
       </c>
       <c r="B4" t="n">
-        <v>99099</v>
+        <v>43319</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220093</v>
+        <v>201146</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Schneider, 1792)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490158</v>
+        <v>489967</v>
       </c>
       <c r="R4" t="n">
-        <v>6995775</v>
+        <v>6996029</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,17 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>3 ex</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,16 +980,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134667203</t>
+          <t>https://artportalen.se/Sighting/135260408</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134667289</v>
+        <v>135251761</v>
       </c>
       <c r="B5" t="n">
-        <v>110150</v>
+        <v>99276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,34 +997,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220294</v>
+        <v>219811</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällskära</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saussurea alpina</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) DC.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490122</v>
+        <v>490003</v>
       </c>
       <c r="R5" t="n">
-        <v>6995824</v>
+        <v>6995966</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,17 +1055,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,16 +1086,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134667289</t>
+          <t>https://artportalen.se/Sighting/135251761</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134667293</v>
+        <v>135251864</v>
       </c>
       <c r="B6" t="n">
-        <v>110150</v>
+        <v>99276</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,34 +1103,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220294</v>
+        <v>219811</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällskära</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saussurea alpina</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) DC.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490042</v>
+        <v>490193</v>
       </c>
       <c r="R6" t="n">
-        <v>6995958</v>
+        <v>6995759</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1173,17 +1161,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,16 +1192,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134667293</t>
+          <t>https://artportalen.se/Sighting/135251864</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134667359</v>
+        <v>135251865</v>
       </c>
       <c r="B7" t="n">
-        <v>110150</v>
+        <v>99276</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,34 +1209,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220294</v>
+        <v>219811</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällskära</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saussurea alpina</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) DC.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490132</v>
+        <v>490185</v>
       </c>
       <c r="R7" t="n">
-        <v>6995842</v>
+        <v>6995767</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1280,17 +1267,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,16 +1298,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134667359</t>
+          <t>https://artportalen.se/Sighting/135251865</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134667263</v>
+        <v>135251867</v>
       </c>
       <c r="B8" t="n">
-        <v>100806</v>
+        <v>99276</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,34 +1315,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222584</v>
+        <v>219811</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bergsslok</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Melica nutans</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490137</v>
+        <v>490175</v>
       </c>
       <c r="R8" t="n">
-        <v>6995833</v>
+        <v>6995781</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1387,17 +1373,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,16 +1404,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134667263</t>
+          <t>https://artportalen.se/Sighting/135251867</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134667291</v>
+        <v>135251868</v>
       </c>
       <c r="B9" t="n">
-        <v>100806</v>
+        <v>99276</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1440,34 +1421,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222584</v>
+        <v>219811</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bergsslok</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Melica nutans</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490082</v>
+        <v>490171</v>
       </c>
       <c r="R9" t="n">
-        <v>6995886</v>
+        <v>6995790</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1494,17 +1479,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1530,16 +1510,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134667291</t>
+          <t>https://artportalen.se/Sighting/135251868</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134667258</v>
+        <v>135251869</v>
       </c>
       <c r="B10" t="n">
-        <v>99472</v>
+        <v>99276</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,34 +1527,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222812</v>
+        <v>219811</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490025</v>
+        <v>490109</v>
       </c>
       <c r="R10" t="n">
-        <v>6996032</v>
+        <v>6995869</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1601,17 +1585,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1637,16 +1616,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134667258</t>
+          <t>https://artportalen.se/Sighting/135251869</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134667286</v>
+        <v>135251871</v>
       </c>
       <c r="B11" t="n">
-        <v>99472</v>
+        <v>99276</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,34 +1633,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222812</v>
+        <v>219811</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490160</v>
+        <v>490100</v>
       </c>
       <c r="R11" t="n">
-        <v>6995755</v>
+        <v>6995889</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1708,17 +1691,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1744,16 +1722,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134667286</t>
+          <t>https://artportalen.se/Sighting/135251871</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134667288</v>
+        <v>135251873</v>
       </c>
       <c r="B12" t="n">
-        <v>102871</v>
+        <v>99276</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,34 +1739,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223037</v>
+        <v>219811</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Humleblomster</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Geum rivale</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490122</v>
+        <v>490070</v>
       </c>
       <c r="R12" t="n">
-        <v>6995824</v>
+        <v>6995932</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1815,17 +1797,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1851,7 +1828,8722 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135251873</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135251876</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>490049</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6995960</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251876</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135251878</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>490030</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6996016</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251878</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135251879</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>490020</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6996030</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251879</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135251880</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>490019</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6996035</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251880</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135251881</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>490014</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6996047</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251881</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135251882</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>490011</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6996051</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251882</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135251884</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>490003</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6996072</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251884</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135251885</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>490009</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6996061</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251885</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135251886</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>489996</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6996048</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251886</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135251888</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>490010</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6996013</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251888</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135251889</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>490016</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6996007</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251889</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135251891</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>490024</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6995989</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251891</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135251892</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>490034</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6995967</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251892</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135251893</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>490074</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6995898</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251893</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135251894</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>490081</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6995890</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251894</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135251895</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>490083</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6995883</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251895</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135251896</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>490088</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6995880</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251896</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135251897</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>490090</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6995873</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251897</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135251899</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>490102</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6995859</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251899</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135251901</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>490105</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6995849</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251901</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135251902</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>490111</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6995844</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251902</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135251904</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>490111</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6995837</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251904</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135251905</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>490117</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6995827</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251905</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135251906</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>490124</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6995819</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251906</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135251907</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>490125</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6995817</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251907</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135251909</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>490131</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6995807</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251909</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135251910</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>490134</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6995801</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251910</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135251911</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>490140</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6995797</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251911</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135251912</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>490140</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6995790</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251912</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135251913</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>490146</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6995783</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251913</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135251914</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>490154</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6995774</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251914</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135251915</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>490159</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6995770</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251915</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135251916</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>490163</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6995766</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251916</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135251917</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>490173</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6995759</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251917</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135251918</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>490176</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6995750</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251918</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135251730</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99298</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>490137</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6995784</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251730</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135251732</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99298</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>490137</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6995777</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Noterad</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251732</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135251734</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99298</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>490143</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6995765</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251734</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135251736</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99298</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>490148</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6995762</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251736</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135251866</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99298</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>490173</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6995778</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251866</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135251874</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99298</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>490050</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6995959</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251874</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135251898</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99298</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>490090</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6995871</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251898</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135251900</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99298</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>490105</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6995849</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251900</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135251903</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99298</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>490111</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6995840</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251903</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135251908</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99298</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>490129</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6995810</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251908</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>134667257</v>
+      </c>
+      <c r="B58" t="n">
+        <v>107943</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>219933</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Kattfot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Antennaria dioica</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>490011</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6996049</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134667257</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>134667264</v>
+      </c>
+      <c r="B59" t="n">
+        <v>108205</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>490172</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6995778</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134667264</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135259562</v>
+      </c>
+      <c r="B60" t="n">
+        <v>108292</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>490137</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6995770</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259562</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135259708</v>
+      </c>
+      <c r="B61" t="n">
+        <v>108292</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>489986</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6996067</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259708</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135259727</v>
+      </c>
+      <c r="B62" t="n">
+        <v>108292</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>490028</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6995963</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259727</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135259737</v>
+      </c>
+      <c r="B63" t="n">
+        <v>108292</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>489990</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6996028</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259737</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>134667203</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99099</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>490158</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6995775</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>3 ex</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134667203</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135251727</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99178</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>490159</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6995759</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251727</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135259548</v>
+      </c>
+      <c r="B66" t="n">
+        <v>108362</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220102</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Kärrfibbla</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Crepis paludosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>490145</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6995771</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259548</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>134667289</v>
+      </c>
+      <c r="B67" t="n">
+        <v>110150</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220294</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Fjällskära</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Saussurea alpina</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) DC.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>490122</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6995824</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134667289</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>134667293</v>
+      </c>
+      <c r="B68" t="n">
+        <v>110150</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220294</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Fjällskära</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Saussurea alpina</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) DC.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>490042</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6995958</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134667293</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>134667359</v>
+      </c>
+      <c r="B69" t="n">
+        <v>110150</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220294</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Fjällskära</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Saussurea alpina</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) DC.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>490132</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6995842</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134667359</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135259550</v>
+      </c>
+      <c r="B70" t="n">
+        <v>103845</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>490110</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6995828</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259550</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135259552</v>
+      </c>
+      <c r="B71" t="n">
+        <v>103845</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>490121</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6995803</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259552</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>135259553</v>
+      </c>
+      <c r="B72" t="n">
+        <v>104793</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>490135</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6995783</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259553</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135259728</v>
+      </c>
+      <c r="B73" t="n">
+        <v>104793</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>490023</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6995970</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259728</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135259549</v>
+      </c>
+      <c r="B74" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>490110</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6995828</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259549</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135259551</v>
+      </c>
+      <c r="B75" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>490118</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6995807</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259551</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135259566</v>
+      </c>
+      <c r="B76" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>490155</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6995762</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259566</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>135259724</v>
+      </c>
+      <c r="B77" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>490047</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6995923</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259724</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>135259726</v>
+      </c>
+      <c r="B78" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>490028</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6995963</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259726</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>135259730</v>
+      </c>
+      <c r="B79" t="n">
+        <v>101483</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>490021</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6995979</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259730</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>134667263</v>
+      </c>
+      <c r="B80" t="n">
+        <v>100806</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>490137</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6995833</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134667263</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>134667291</v>
+      </c>
+      <c r="B81" t="n">
+        <v>100806</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>490082</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6995886</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134667291</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>135259556</v>
+      </c>
+      <c r="B82" t="n">
+        <v>100886</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>490135</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6995775</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259556</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>135259722</v>
+      </c>
+      <c r="B83" t="n">
+        <v>100886</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>490047</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6995923</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259722</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>135259729</v>
+      </c>
+      <c r="B84" t="n">
+        <v>101385</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>490021</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6995979</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259729</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>134667258</v>
+      </c>
+      <c r="B85" t="n">
+        <v>99472</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>490025</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6996032</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134667258</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>134667286</v>
+      </c>
+      <c r="B86" t="n">
+        <v>99472</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>490160</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6995755</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134667286</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>135259542</v>
+      </c>
+      <c r="B87" t="n">
+        <v>99551</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>490180</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6995779</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259542</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>135259560</v>
+      </c>
+      <c r="B88" t="n">
+        <v>99551</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>490137</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6995770</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259560</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>134667288</v>
+      </c>
+      <c r="B89" t="n">
+        <v>102871</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>223037</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Humleblomster</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Geum rivale</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>E14 Brunflo - Grytan - Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>490122</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6995824</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>NVI åt Trafikverket ny G/C-väg Brunflo - Optand</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/134667288</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>135259565</v>
+      </c>
+      <c r="B90" t="n">
+        <v>102954</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>223037</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Humleblomster</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Geum rivale</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>490141</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6995767</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259565</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>135259709</v>
+      </c>
+      <c r="B91" t="n">
+        <v>102954</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>223037</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Humleblomster</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Geum rivale</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>489988</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6996054</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259709</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>135259720</v>
+      </c>
+      <c r="B92" t="n">
+        <v>102954</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>223037</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Humleblomster</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Geum rivale</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>490075</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6995889</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259720</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>135259546</v>
+      </c>
+      <c r="B93" t="n">
+        <v>99080</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>490150</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6995761</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259546</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>135251877</v>
+      </c>
+      <c r="B94" t="n">
+        <v>99184</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>223572</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Blodnycklar</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Dactylorhiza incarnata var. cruenta</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(O F.Müll.) Hyl.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>490029</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6996006</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135251877</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>135259713</v>
+      </c>
+      <c r="B95" t="n">
+        <v>95916</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>1004672</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Källmossor</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Philonotis</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Brid.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>E14 - Brunflo/Grytan/Optand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>489985</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6996008</v>
+      </c>
+      <c r="S95" t="n">
+        <v>5</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135259713</t>
         </is>
       </c>
     </row>
@@ -1868,6 +10560,89 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17456-2026 artfynd.xlsx
+++ b/artfynd/A 17456-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135259564</v>
       </c>
       <c r="B2" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135259731</v>
       </c>
       <c r="B3" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135251761</v>
       </c>
       <c r="B5" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>135251864</v>
       </c>
       <c r="B6" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>135251865</v>
       </c>
       <c r="B7" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>135251867</v>
       </c>
       <c r="B8" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>135251868</v>
       </c>
       <c r="B9" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>135251869</v>
       </c>
       <c r="B10" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>135251871</v>
       </c>
       <c r="B11" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>135251873</v>
       </c>
       <c r="B12" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>135251876</v>
       </c>
       <c r="B13" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>135251878</v>
       </c>
       <c r="B14" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>135251879</v>
       </c>
       <c r="B15" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>135251880</v>
       </c>
       <c r="B16" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>135251881</v>
       </c>
       <c r="B17" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>135251882</v>
       </c>
       <c r="B18" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>135251884</v>
       </c>
       <c r="B19" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>135251885</v>
       </c>
       <c r="B20" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>135251886</v>
       </c>
       <c r="B21" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>135251888</v>
       </c>
       <c r="B22" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>135251889</v>
       </c>
       <c r="B23" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>135251891</v>
       </c>
       <c r="B24" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>135251892</v>
       </c>
       <c r="B25" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>135251893</v>
       </c>
       <c r="B26" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>135251894</v>
       </c>
       <c r="B27" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>135251895</v>
       </c>
       <c r="B28" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>135251896</v>
       </c>
       <c r="B29" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>135251897</v>
       </c>
       <c r="B30" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>135251899</v>
       </c>
       <c r="B31" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>135251901</v>
       </c>
       <c r="B32" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>135251902</v>
       </c>
       <c r="B33" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>135251904</v>
       </c>
       <c r="B34" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>135251905</v>
       </c>
       <c r="B35" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>135251906</v>
       </c>
       <c r="B36" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>135251907</v>
       </c>
       <c r="B37" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>135251909</v>
       </c>
       <c r="B38" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>135251910</v>
       </c>
       <c r="B39" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>135251911</v>
       </c>
       <c r="B40" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>135251912</v>
       </c>
       <c r="B41" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>135251913</v>
       </c>
       <c r="B42" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>135251914</v>
       </c>
       <c r="B43" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>135251915</v>
       </c>
       <c r="B44" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>135251916</v>
       </c>
       <c r="B45" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         <v>135251917</v>
       </c>
       <c r="B46" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>135251918</v>
       </c>
       <c r="B47" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>135251730</v>
       </c>
       <c r="B48" t="n">
-        <v>99298</v>
+        <v>99300</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         <v>135251732</v>
       </c>
       <c r="B49" t="n">
-        <v>99298</v>
+        <v>99300</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>135251734</v>
       </c>
       <c r="B50" t="n">
-        <v>99298</v>
+        <v>99300</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>135251736</v>
       </c>
       <c r="B51" t="n">
-        <v>99298</v>
+        <v>99300</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>135251866</v>
       </c>
       <c r="B52" t="n">
-        <v>99298</v>
+        <v>99300</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6078,7 +6078,7 @@
         <v>135251874</v>
       </c>
       <c r="B53" t="n">
-        <v>99298</v>
+        <v>99300</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>135251898</v>
       </c>
       <c r="B54" t="n">
-        <v>99298</v>
+        <v>99300</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>135251900</v>
       </c>
       <c r="B55" t="n">
-        <v>99298</v>
+        <v>99300</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>135251903</v>
       </c>
       <c r="B56" t="n">
-        <v>99298</v>
+        <v>99300</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>135251908</v>
       </c>
       <c r="B57" t="n">
-        <v>99298</v>
+        <v>99300</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>135259562</v>
       </c>
       <c r="B60" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>135259708</v>
       </c>
       <c r="B61" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>135259727</v>
       </c>
       <c r="B62" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>135259737</v>
       </c>
       <c r="B63" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>135251727</v>
       </c>
       <c r="B65" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>135259548</v>
       </c>
       <c r="B66" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>135259550</v>
       </c>
       <c r="B70" t="n">
-        <v>103845</v>
+        <v>103847</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>135259552</v>
       </c>
       <c r="B71" t="n">
-        <v>103845</v>
+        <v>103847</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         <v>135259553</v>
       </c>
       <c r="B72" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         <v>135259728</v>
       </c>
       <c r="B73" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>135259549</v>
       </c>
       <c r="B74" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>135259551</v>
       </c>
       <c r="B75" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>135259566</v>
       </c>
       <c r="B76" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>135259724</v>
       </c>
       <c r="B77" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>135259726</v>
       </c>
       <c r="B78" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>135259730</v>
       </c>
       <c r="B79" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>135259556</v>
       </c>
       <c r="B82" t="n">
-        <v>100886</v>
+        <v>100888</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>135259722</v>
       </c>
       <c r="B83" t="n">
-        <v>100886</v>
+        <v>100888</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>135259729</v>
       </c>
       <c r="B84" t="n">
-        <v>101385</v>
+        <v>101387</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         <v>135259542</v>
       </c>
       <c r="B87" t="n">
-        <v>99551</v>
+        <v>99553</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>135259560</v>
       </c>
       <c r="B88" t="n">
-        <v>99551</v>
+        <v>99553</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>135259565</v>
       </c>
       <c r="B90" t="n">
-        <v>102954</v>
+        <v>102956</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
         <v>135259709</v>
       </c>
       <c r="B91" t="n">
-        <v>102954</v>
+        <v>102956</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>135259720</v>
       </c>
       <c r="B92" t="n">
-        <v>102954</v>
+        <v>102956</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>135259546</v>
       </c>
       <c r="B93" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>135251877</v>
       </c>
       <c r="B94" t="n">
-        <v>99184</v>
+        <v>99186</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>135259713</v>
       </c>
       <c r="B95" t="n">
-        <v>95916</v>
+        <v>95918</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
